--- a/VerveStacks_CHN_grids_kan60/SysSettings.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C922019-EAAB-451B-B369-01C2A3033C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33839D6-8136-463A-B90F-510242657EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -6236,7 +6236,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7886F1C4-9168-4285-B1BA-BC99E58BBF5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72CE26F2-95C1-49DF-AEFD-CA6517086306}">
   <dimension ref="B3:H112"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8758,7 +8758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6026A44E-DE43-447F-B6A0-1397EAFABD4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858054C7-8048-4255-960F-D863F11F68BF}">
   <dimension ref="B3:I63"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10333,7 +10333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06AD4F7B-2D34-486F-9063-03826C0D087A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9263028-8475-48D8-B9FC-3F615B26DDC4}">
   <dimension ref="B3:I63"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan60/SysSettings.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33839D6-8136-463A-B90F-510242657EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662D3B68-0794-4925-B52B-73A8E165982A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6236,7 +6236,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72CE26F2-95C1-49DF-AEFD-CA6517086306}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22013D5A-AF6F-4BEC-B308-89033B551D4E}">
   <dimension ref="B3:H112"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8758,7 +8758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858054C7-8048-4255-960F-D863F11F68BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95720F70-E6F4-4142-B179-56E10856D245}">
   <dimension ref="B3:I63"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10333,7 +10333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9263028-8475-48D8-B9FC-3F615B26DDC4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8BCAB6-E311-4C4C-ABCD-60B2FB56FE25}">
   <dimension ref="B3:I63"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan60/SysSettings.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662D3B68-0794-4925-B52B-73A8E165982A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC630FF-D8CB-4211-830D-4ABE631F61F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6236,7 +6236,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22013D5A-AF6F-4BEC-B308-89033B551D4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D521347-E035-4A74-B891-EA4ACEE51AAE}">
   <dimension ref="B3:H112"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8758,7 +8758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95720F70-E6F4-4142-B179-56E10856D245}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7927D824-18B1-4060-BB4B-D68477A6E320}">
   <dimension ref="B3:I63"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10333,7 +10333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8BCAB6-E311-4C4C-ABCD-60B2FB56FE25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD7EC112-E280-43E4-AE53-23CE11889A96}">
   <dimension ref="B3:I63"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan60/SysSettings.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC630FF-D8CB-4211-830D-4ABE631F61F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE836788-0790-4E8A-A3DE-2F1A7CA7C2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6236,7 +6236,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D521347-E035-4A74-B891-EA4ACEE51AAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC22C15-21BC-43DB-85AA-E0671460D37A}">
   <dimension ref="B3:H112"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8758,7 +8758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7927D824-18B1-4060-BB4B-D68477A6E320}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AE333E3-FFC0-41D3-A519-E35F8EF38D08}">
   <dimension ref="B3:I63"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10333,7 +10333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD7EC112-E280-43E4-AE53-23CE11889A96}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D5E02F5-0931-454D-868B-022329E96EFD}">
   <dimension ref="B3:I63"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan60/SysSettings.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE836788-0790-4E8A-A3DE-2F1A7CA7C2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D5681D1-6D16-4567-9CC0-D954591D49FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -6236,7 +6236,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC22C15-21BC-43DB-85AA-E0671460D37A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1AC498-D252-4736-9601-55300A488AFF}">
   <dimension ref="B3:H112"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8758,7 +8758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AE333E3-FFC0-41D3-A519-E35F8EF38D08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2F55D6-8573-442C-A4FE-6339B1A2C721}">
   <dimension ref="B3:I63"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10333,7 +10333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D5E02F5-0931-454D-868B-022329E96EFD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1D2F5DB-BEE8-4682-B068-173ECA6BF973}">
   <dimension ref="B3:I63"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan60/SysSettings.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D5681D1-6D16-4567-9CC0-D954591D49FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BF54DD-ACB8-48AD-9466-96AF20009177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -6236,7 +6236,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1AC498-D252-4736-9601-55300A488AFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD72D76-DC28-4620-A87D-9FE864D14AA4}">
   <dimension ref="B3:H112"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8758,7 +8758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2F55D6-8573-442C-A4FE-6339B1A2C721}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{071AF05D-624A-43F3-B1DA-462FA622B096}">
   <dimension ref="B3:I63"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10333,7 +10333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1D2F5DB-BEE8-4682-B068-173ECA6BF973}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE466029-CB74-4283-A956-BDB891269CBB}">
   <dimension ref="B3:I63"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
